--- a/data/processed/pims_subsystem_document.xlsx
+++ b/data/processed/pims_subsystem_document.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1168"/>
+  <dimension ref="A1:C1243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20263,12 +20263,1287 @@
       </c>
       <c r="B1168" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-70-HOP-3194-90-01</t>
+          <t>PR2ME-PIL-QTY-59-HOP-3310-08-01</t>
         </is>
       </c>
       <c r="C1168" t="inlineStr">
         <is>
-          <t>3194-90-01</t>
+          <t>3310-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-FC-3310-08-01</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>3310-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3310-08-01</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>3310-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3310-09-01</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>3310-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-FC-3310-09-01</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>3310-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3310-09-01</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>3310-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3310-17-03</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>3310-17-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-FC-3310-17-03</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>3310-17-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3310-17-03</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>3310-17-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3310-17-03</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>3310-17-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3510-01-01</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>3510-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-SP-3510-01-01</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>3510-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3510-01-01</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>3510-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3510-01-01</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>3510-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3510-04-01</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>3510-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-CC-3510-04-01</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>3510-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3510-04-01</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>3510-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3530-01-04</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>3530-01-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-CC-3530-01-04</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>3530-01-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3530-01-04</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>3530-01-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3410-06-02</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>3410-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-FC-3410-06-02</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>3410-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3410-06-02</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>3410-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3410-06-02</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>3410-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3420-15-02</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>3420-15-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-PRW-3420-15-02</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>3420-15-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3420-15-02</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>3420-15-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3120-02-01</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>3120-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-PRW-3120-02-01</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>3120-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3120-02-01</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>3120-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3110-02-03</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>3110-02-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-CY-3110-02-03</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>3110-02-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3110-02-03</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>3110-02-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3110-02-03</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>3110-02-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-2320-01-02</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>2320-01-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-SP-2320-01-02</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>2320-01-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2320-01-02</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>2320-01-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-2320-01-02</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>2320-01-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-2320-01-04</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>2320-01-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2320-01-04</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>2320-01-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-2320-02-05</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>2320-02-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-2320-02-05</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>2320-02-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2310-05-02</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>2310-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2310-06-02</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>2310-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2310-07-02</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>2310-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-2120-01-02</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>2120-01-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-FW-2120-01-02</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>2120-01-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2120-01-02</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>2120-01-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-2120-01-01</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>2120-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-FW-2120-01-01</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>2120-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-2120-01-01</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>2120-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-2110-90-09</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>2110-90-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-2110-90-09</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>2110-90-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-2100-01-03</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>2100-01-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2100-01-01</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>2100-01-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-2100-01-02</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>2100-01-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2100-01-01</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>2100-01-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3580-02-04</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>3580-02-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-FL-3580-02-04</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>3580-02-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3580-02-04</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>3580-02-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3580-07-01</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>3580-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-ML-3580-07-01</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>3580-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3580-07-01</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>3580-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3580-07-01</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>3580-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3580-08-04</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>3580-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-GWP-3580-08-04</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>3580-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3580-08-04</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>3580-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3580-08-04</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>3580-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-2100-01-01</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>2100-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-AP-2100-01-01</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>2100-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2100-01-01</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>2100-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-2191-50-09</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>2191-50-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2114-90-01</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>2114-90-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3191-90-01</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>3191-90-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3193-90-01</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>3193-90-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3591-90-01</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>3591-90-01</t>
         </is>
       </c>
     </row>

--- a/data/processed/pims_subsystem_document.xlsx
+++ b/data/processed/pims_subsystem_document.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1243"/>
+  <dimension ref="A1:C1268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21538,12 +21538,437 @@
       </c>
       <c r="B1243" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-70-HOP-3591-90-01</t>
+          <t>PR2ME-PIL-QTY-59-HOP-3310-21-02</t>
         </is>
       </c>
       <c r="C1243" t="inlineStr">
         <is>
-          <t>3591-90-01</t>
+          <t>3310-21-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-FT-3310-21-02</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>3310-21-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3310-21-02</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>3310-21-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3310-21-02</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>3310-21-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3210-01-01</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>3210-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3210-01-01</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>3210-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3410-02-02</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>3410-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-FC-3410-02-02</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>3410-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3410-02-02</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>3410-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3410-02-02</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>3410-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3410-11-03</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>3410-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-FT-3410-11-03</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>3410-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3410-11-03</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>3410-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3410-11-03</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>3410-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3410-16-02</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>3410-16-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-FC-3410-16-02</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>3410-16-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3410-16-02</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>3410-16-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3410-16-02</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>3410-16-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3000-02-01</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>3000-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-PRW-3000-02-01</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>3000-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-4110-03-01</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>2110-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-2110-01-01</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>2110-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-2110-01-01</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>2110-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2110-01-01</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>2110-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-4130-90-01</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>4130-90-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-4130-90-01</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>4130-90-01</t>
         </is>
       </c>
     </row>

--- a/data/processed/pims_subsystem_document.xlsx
+++ b/data/processed/pims_subsystem_document.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1268"/>
+  <dimension ref="A1:C1291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21951,7 +21951,7 @@
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>4130-90-01</t>
+          <t>2120-90-09</t>
         </is>
       </c>
     </row>
@@ -21963,12 +21963,403 @@
       </c>
       <c r="B1268" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-65-HOP-4130-90-01</t>
+          <t>PR2ME-PIL-QTY-59-HOP-2120-90-09</t>
         </is>
       </c>
       <c r="C1268" t="inlineStr">
         <is>
-          <t>4130-90-01</t>
+          <t>2120-90-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-2120-90-09</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>2120-90-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-KC-3160-03-02</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>3160-03-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3160-03-02</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>3160-03-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-CC-3510-03-06</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>3510-03-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3510-03-06</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>3510-03-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3420-13-02</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>3420-13-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-FT-3420-13-02</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>3420-13-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3420-13-02</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>3420-13-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3420-13-02</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>3420-13-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3140-01-01</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>3140-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3140-01-01</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>3140-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3140-01-01</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>3140-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3220-07-02</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>3220-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3220-07-02</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>3220-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3580-05-01</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>3580-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-GWF-3580-05-01</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>3580-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3580-05-01</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>3580-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3580-05-01</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>3580-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3580-07-03</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>3580-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-ML-3580-07-03</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>3580-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3580-07-03</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>3580-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3580-07-03</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>3580-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>PR2ME-COM</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2191-90-01</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>2191-90-01</t>
         </is>
       </c>
     </row>
